--- a/тестирование API admin.xlsx
+++ b/тестирование API admin.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22545" windowHeight="12090"/>
+    <workbookView windowWidth="28800" windowHeight="12405"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,6 +35,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -71,6 +78,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -113,6 +127,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -140,6 +161,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -164,6 +192,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -188,6 +223,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -221,6 +263,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -245,6 +294,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -281,6 +337,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -305,6 +368,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -327,6 +397,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -357,6 +434,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -381,6 +465,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -408,6 +499,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -426,6 +524,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -441,6 +546,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -456,6 +568,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -474,6 +593,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -501,6 +627,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -516,6 +649,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -540,6 +680,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -558,6 +705,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -576,6 +730,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -594,6 +755,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -609,6 +777,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -627,6 +802,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -645,6 +827,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -666,6 +855,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -687,6 +883,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -708,6 +911,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -723,6 +933,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -738,6 +955,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -753,6 +977,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>﻿</t>
     </r>
     <r>
@@ -781,10 +1012,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -795,9 +1026,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -810,6 +1049,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -818,15 +1066,22 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -840,55 +1095,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -903,21 +1125,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -932,8 +1140,31 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -955,49 +1186,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1009,7 +1324,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1021,7 +1348,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1033,109 +1366,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1146,6 +1377,65 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1174,21 +1464,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -1202,197 +1477,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1405,55 +1636,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="40% — Акцент6" xfId="1" builtinId="51"/>
+    <cellStyle name="Акцент4" xfId="2" builtinId="41"/>
+    <cellStyle name="20% — Акцент6" xfId="3" builtinId="50"/>
+    <cellStyle name="Гиперссылка" xfId="4" builtinId="8"/>
+    <cellStyle name="40% — Акцент5" xfId="5" builtinId="47"/>
+    <cellStyle name="Акцент3" xfId="6" builtinId="37"/>
+    <cellStyle name="20% — Акцент5" xfId="7" builtinId="46"/>
+    <cellStyle name="Акцент2" xfId="8" builtinId="33"/>
+    <cellStyle name="20% — Акцент4" xfId="9" builtinId="42"/>
+    <cellStyle name="Заголовок 2" xfId="10" builtinId="17"/>
+    <cellStyle name="60% — Акцент3" xfId="11" builtinId="40"/>
+    <cellStyle name="Акцент1" xfId="12" builtinId="29"/>
+    <cellStyle name="20% — Акцент3" xfId="13" builtinId="38"/>
+    <cellStyle name="Заголовок 1" xfId="14" builtinId="16"/>
+    <cellStyle name="Денежный" xfId="15" builtinId="4"/>
+    <cellStyle name="60% — Акцент2" xfId="16" builtinId="36"/>
+    <cellStyle name="Ввод" xfId="17" builtinId="20"/>
+    <cellStyle name="Акцент6" xfId="18" builtinId="49"/>
+    <cellStyle name="Процент" xfId="19" builtinId="5"/>
+    <cellStyle name="40% — Акцент2" xfId="20" builtinId="35"/>
+    <cellStyle name="20% — Акцент2" xfId="21" builtinId="34"/>
+    <cellStyle name="Запятая" xfId="22" builtinId="3"/>
+    <cellStyle name="Акцент5" xfId="23" builtinId="45"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="40% — Акцент1" xfId="25" builtinId="31"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="27" builtinId="9"/>
+    <cellStyle name="Связанная ячейка" xfId="28" builtinId="24"/>
+    <cellStyle name="Проверить ячейку" xfId="29" builtinId="23"/>
+    <cellStyle name="60% — Акцент5" xfId="30" builtinId="48"/>
+    <cellStyle name="Заголовок 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Заголовок 3" xfId="32" builtinId="18"/>
+    <cellStyle name="60% — Акцент4" xfId="33" builtinId="44"/>
+    <cellStyle name="Плохой" xfId="34" builtinId="27"/>
+    <cellStyle name="Вычисление" xfId="35" builtinId="22"/>
+    <cellStyle name="60% — Акцент6" xfId="36" builtinId="52"/>
+    <cellStyle name="Денежный [0]" xfId="37" builtinId="7"/>
+    <cellStyle name="Пояснительный текст" xfId="38" builtinId="53"/>
+    <cellStyle name="40% — Акцент3" xfId="39" builtinId="39"/>
+    <cellStyle name="Заголовок" xfId="40" builtinId="15"/>
+    <cellStyle name="Запятая [0]" xfId="41" builtinId="6"/>
+    <cellStyle name="Итого" xfId="42" builtinId="25"/>
+    <cellStyle name="Предупреждающий текст" xfId="43" builtinId="11"/>
+    <cellStyle name="Примечание" xfId="44" builtinId="10"/>
+    <cellStyle name="60% — Акцент1" xfId="45" builtinId="32"/>
+    <cellStyle name="Хороший" xfId="46" builtinId="26"/>
+    <cellStyle name="40% — Акцент4" xfId="47" builtinId="43"/>
+    <cellStyle name="Вывод" xfId="48" builtinId="21"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1723,14 +1954,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="13.85" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="59.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="28.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="24.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="20.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="31.4285714285714" customWidth="1"/>
-    <col min="7" max="7" width="28.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="59.7166666666667" customWidth="1"/>
+    <col min="3" max="3" width="28.425" customWidth="1"/>
+    <col min="4" max="4" width="24.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="20.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="31.425" customWidth="1"/>
+    <col min="7" max="7" width="28.8583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="4:6">
@@ -1752,7 +1983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" ht="18.75" spans="1:5">
+    <row r="3" ht="26.25" spans="1:5">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1769,7 +2000,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="18.75" spans="1:7">
+    <row r="4" ht="26.25" spans="1:7">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1792,7 +2023,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="18.75" spans="1:6">
+    <row r="5" ht="26.25" spans="1:6">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1812,7 +2043,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="18.75" spans="1:8">
+    <row r="6" ht="26.25" spans="1:8">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1835,7 +2066,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" ht="18.75" spans="1:7">
+    <row r="7" ht="26.25" spans="1:7">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1858,7 +2089,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="18.75" spans="1:8">
+    <row r="8" ht="26.25" spans="1:8">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1881,7 +2112,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" ht="18.75" spans="1:6">
+    <row r="9" ht="26.25" spans="1:6">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1906,7 +2137,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" ht="18.75" spans="1:5">
+    <row r="13" ht="26.25" spans="1:5">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1923,7 +2154,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" ht="18.75" spans="1:8">
+    <row r="14" ht="26.25" spans="1:8">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1946,7 +2177,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" ht="18.75" spans="1:6">
+    <row r="15" ht="26.25" spans="1:6">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -1966,7 +2197,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" ht="18.75" spans="1:6">
+    <row r="16" ht="26.25" spans="1:6">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1986,7 +2217,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" ht="18.75" spans="1:7">
+    <row r="17" ht="26.25" spans="1:7">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -2006,7 +2237,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" ht="18.75" spans="1:5">
+    <row r="18" ht="26.25" spans="1:5">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2023,7 +2254,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" ht="18.75" spans="1:6">
+    <row r="19" ht="26.25" spans="1:6">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -2040,7 +2271,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="20" ht="18.75" spans="1:6">
+    <row r="20" ht="26.25" spans="1:6">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2057,7 +2288,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" ht="105" spans="1:6">
+    <row r="21" ht="83.25" spans="1:6">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2071,7 +2302,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" ht="18.75" spans="1:6">
+    <row r="22" ht="26.25" spans="1:6">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -2088,7 +2319,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" ht="120" spans="1:6">
+    <row r="23" ht="97.15" spans="1:6">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -2105,7 +2336,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" ht="18.75" spans="1:7">
+    <row r="24" ht="26.25" spans="1:7">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -2125,7 +2356,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" ht="18.75" spans="1:7">
+    <row r="25" ht="26.25" spans="1:7">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -2150,7 +2381,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" ht="18.75" spans="1:5">
+    <row r="28" ht="26.25" spans="1:5">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -2161,7 +2392,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" ht="18.75" spans="1:2">
+    <row r="29" ht="26.25" spans="1:2">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -2169,7 +2400,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" ht="18.75" spans="1:2">
+    <row r="30" ht="26.25" spans="1:2">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -2177,7 +2408,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" ht="18.75" spans="1:2">
+    <row r="31" ht="26.25" spans="1:2">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -2185,7 +2416,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" ht="18.75" spans="1:2">
+    <row r="32" ht="26.25" spans="1:2">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -2193,7 +2424,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33" ht="18.75" spans="1:2">
+    <row r="33" ht="26.25" spans="1:2">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -2206,7 +2437,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" ht="18.75" spans="1:5">
+    <row r="36" ht="26.25" spans="1:5">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -2223,7 +2454,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="37" ht="18.75" spans="1:6">
+    <row r="37" ht="26.25" spans="1:6">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -2240,7 +2471,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="38" ht="18.75" spans="1:5">
+    <row r="38" ht="26.25" spans="1:5">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -2257,7 +2488,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" ht="18.75" spans="1:5">
+    <row r="39" ht="26.25" spans="1:5">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -2274,7 +2505,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" ht="18.75" spans="1:5">
+    <row r="40" ht="26.25" spans="1:5">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -2291,7 +2522,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" ht="18.75" spans="1:5">
+    <row r="41" ht="26.25" spans="1:5">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -2305,7 +2536,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="42" ht="18.75" spans="1:5">
+    <row r="42" ht="26.25" spans="1:5">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -2319,7 +2550,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="43" ht="18.75" spans="1:5">
+    <row r="43" ht="26.25" spans="1:5">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -2333,7 +2564,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="44" ht="18.75" spans="1:5">
+    <row r="44" ht="26.25" spans="1:5">
       <c r="A44" t="s">
         <v>28</v>
       </c>
@@ -2347,7 +2578,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" ht="18.75" spans="1:5">
+    <row r="45" ht="26.25" spans="1:5">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -2361,7 +2592,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="46" ht="18.75" spans="1:5">
+    <row r="46" ht="26.25" spans="1:5">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -2375,7 +2606,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" ht="18.75" spans="1:5">
+    <row r="47" ht="26.25" spans="1:5">
       <c r="A47" t="s">
         <v>28</v>
       </c>
@@ -2389,7 +2620,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" ht="18.75" spans="1:5">
+    <row r="48" ht="26.25" spans="1:5">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -2408,7 +2639,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" ht="18.75" spans="1:5">
+    <row r="51" ht="26.25" spans="1:5">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -2422,7 +2653,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" ht="18.75" spans="1:5">
+    <row r="52" ht="26.25" spans="1:5">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -2436,7 +2667,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" ht="18.75" spans="1:5">
+    <row r="53" ht="26.25" spans="1:5">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -2450,7 +2681,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" ht="18.75" spans="1:5">
+    <row r="54" ht="26.25" spans="1:5">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -2461,7 +2692,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="55" ht="75" spans="1:5">
+    <row r="55" ht="69.4" spans="1:5">
       <c r="A55" t="s">
         <v>28</v>
       </c>
@@ -2472,7 +2703,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="56" ht="60" spans="1:5">
+    <row r="56" ht="55.5" spans="1:5">
       <c r="A56" t="s">
         <v>28</v>
       </c>
@@ -2483,7 +2714,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="57" ht="60" spans="1:5">
+    <row r="57" ht="55.5" spans="1:5">
       <c r="A57" t="s">
         <v>28</v>
       </c>
@@ -2494,7 +2725,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="58" ht="60" spans="1:5">
+    <row r="58" ht="55.5" spans="1:5">
       <c r="A58" t="s">
         <v>28</v>
       </c>
@@ -2505,7 +2736,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" ht="60" spans="1:5">
+    <row r="59" ht="55.5" spans="1:5">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -2516,7 +2747,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="60" ht="60" spans="1:5">
+    <row r="60" ht="55.5" spans="1:5">
       <c r="A60" t="s">
         <v>28</v>
       </c>

--- a/тестирование API admin.xlsx
+++ b/тестирование API admin.xlsx
@@ -4,17 +4,18 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12405"/>
+    <workbookView windowWidth="22545" windowHeight="12090" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="122">
   <si>
     <t>Корректные данные</t>
   </si>
@@ -1005,6 +1006,21 @@
   </si>
   <si>
     <t>Создание заявки на основе заявки пользователя</t>
+  </si>
+  <si>
+    <t>clients проверен</t>
+  </si>
+  <si>
+    <t>Допроверить:</t>
+  </si>
+  <si>
+    <t>Если у client есть User</t>
+  </si>
+  <si>
+    <t>Если у client есть Ticket</t>
+  </si>
+  <si>
+    <t>Если у client есть userTicket</t>
   </si>
 </sst>
 </file>
@@ -1012,10 +1028,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1023,6 +1039,28 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1034,16 +1072,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1057,9 +1103,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1074,6 +1135,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -1081,7 +1157,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1096,21 +1172,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1124,52 +1186,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1186,91 +1202,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1282,91 +1382,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1384,18 +1400,46 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1411,6 +1455,17 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1438,192 +1493,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1636,55 +1652,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="40% — Акцент6" xfId="1" builtinId="51"/>
-    <cellStyle name="Акцент4" xfId="2" builtinId="41"/>
-    <cellStyle name="20% — Акцент6" xfId="3" builtinId="50"/>
-    <cellStyle name="Гиперссылка" xfId="4" builtinId="8"/>
-    <cellStyle name="40% — Акцент5" xfId="5" builtinId="47"/>
-    <cellStyle name="Акцент3" xfId="6" builtinId="37"/>
-    <cellStyle name="20% — Акцент5" xfId="7" builtinId="46"/>
-    <cellStyle name="Акцент2" xfId="8" builtinId="33"/>
-    <cellStyle name="20% — Акцент4" xfId="9" builtinId="42"/>
-    <cellStyle name="Заголовок 2" xfId="10" builtinId="17"/>
-    <cellStyle name="60% — Акцент3" xfId="11" builtinId="40"/>
-    <cellStyle name="Акцент1" xfId="12" builtinId="29"/>
-    <cellStyle name="20% — Акцент3" xfId="13" builtinId="38"/>
-    <cellStyle name="Заголовок 1" xfId="14" builtinId="16"/>
-    <cellStyle name="Денежный" xfId="15" builtinId="4"/>
-    <cellStyle name="60% — Акцент2" xfId="16" builtinId="36"/>
-    <cellStyle name="Ввод" xfId="17" builtinId="20"/>
-    <cellStyle name="Акцент6" xfId="18" builtinId="49"/>
-    <cellStyle name="Процент" xfId="19" builtinId="5"/>
-    <cellStyle name="40% — Акцент2" xfId="20" builtinId="35"/>
-    <cellStyle name="20% — Акцент2" xfId="21" builtinId="34"/>
-    <cellStyle name="Запятая" xfId="22" builtinId="3"/>
-    <cellStyle name="Акцент5" xfId="23" builtinId="45"/>
-    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
-    <cellStyle name="40% — Акцент1" xfId="25" builtinId="31"/>
-    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="27" builtinId="9"/>
-    <cellStyle name="Связанная ячейка" xfId="28" builtinId="24"/>
-    <cellStyle name="Проверить ячейку" xfId="29" builtinId="23"/>
-    <cellStyle name="60% — Акцент5" xfId="30" builtinId="48"/>
-    <cellStyle name="Заголовок 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Заголовок 3" xfId="32" builtinId="18"/>
-    <cellStyle name="60% — Акцент4" xfId="33" builtinId="44"/>
-    <cellStyle name="Плохой" xfId="34" builtinId="27"/>
-    <cellStyle name="Вычисление" xfId="35" builtinId="22"/>
-    <cellStyle name="60% — Акцент6" xfId="36" builtinId="52"/>
-    <cellStyle name="Денежный [0]" xfId="37" builtinId="7"/>
-    <cellStyle name="Пояснительный текст" xfId="38" builtinId="53"/>
-    <cellStyle name="40% — Акцент3" xfId="39" builtinId="39"/>
-    <cellStyle name="Заголовок" xfId="40" builtinId="15"/>
-    <cellStyle name="Запятая [0]" xfId="41" builtinId="6"/>
-    <cellStyle name="Итого" xfId="42" builtinId="25"/>
-    <cellStyle name="Предупреждающий текст" xfId="43" builtinId="11"/>
-    <cellStyle name="Примечание" xfId="44" builtinId="10"/>
-    <cellStyle name="60% — Акцент1" xfId="45" builtinId="32"/>
-    <cellStyle name="Хороший" xfId="46" builtinId="26"/>
-    <cellStyle name="40% — Акцент4" xfId="47" builtinId="43"/>
-    <cellStyle name="Вывод" xfId="48" builtinId="21"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1954,14 +1970,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="13.85" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="59.7166666666667" customWidth="1"/>
-    <col min="3" max="3" width="28.425" customWidth="1"/>
-    <col min="4" max="4" width="24.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="20.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="31.425" customWidth="1"/>
-    <col min="7" max="7" width="28.8583333333333" customWidth="1"/>
+    <col min="2" max="2" width="59.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="28.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="24.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="20.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="31.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="28.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="4:6">
@@ -1983,7 +1999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" ht="26.25" spans="1:5">
+    <row r="3" ht="18.75" spans="1:5">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2000,7 +2016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="26.25" spans="1:7">
+    <row r="4" ht="18.75" spans="1:7">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2023,7 +2039,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="26.25" spans="1:6">
+    <row r="5" ht="18.75" spans="1:6">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2043,7 +2059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="26.25" spans="1:8">
+    <row r="6" ht="18.75" spans="1:8">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -2066,7 +2082,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" ht="26.25" spans="1:7">
+    <row r="7" ht="18.75" spans="1:7">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -2089,7 +2105,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="26.25" spans="1:8">
+    <row r="8" ht="18.75" spans="1:8">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -2112,7 +2128,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" ht="26.25" spans="1:6">
+    <row r="9" ht="18.75" spans="1:6">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -2137,7 +2153,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" ht="26.25" spans="1:5">
+    <row r="13" ht="18.75" spans="1:5">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -2154,7 +2170,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" ht="26.25" spans="1:8">
+    <row r="14" ht="18.75" spans="1:8">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -2177,7 +2193,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" ht="26.25" spans="1:6">
+    <row r="15" ht="18.75" spans="1:6">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -2197,7 +2213,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" ht="26.25" spans="1:6">
+    <row r="16" ht="18.75" spans="1:6">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -2217,7 +2233,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" ht="26.25" spans="1:7">
+    <row r="17" ht="18.75" spans="1:7">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -2237,7 +2253,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" ht="26.25" spans="1:5">
+    <row r="18" ht="18.75" spans="1:5">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2254,7 +2270,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" ht="26.25" spans="1:6">
+    <row r="19" ht="18.75" spans="1:6">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -2271,7 +2287,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="20" ht="26.25" spans="1:6">
+    <row r="20" ht="18.75" spans="1:6">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2288,7 +2304,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" ht="83.25" spans="1:6">
+    <row r="21" ht="105" spans="1:6">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2302,7 +2318,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" ht="26.25" spans="1:6">
+    <row r="22" ht="18.75" spans="1:6">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -2319,7 +2335,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" ht="97.15" spans="1:6">
+    <row r="23" ht="120" spans="1:6">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -2336,7 +2352,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" ht="26.25" spans="1:7">
+    <row r="24" ht="18.75" spans="1:7">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -2356,7 +2372,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" ht="26.25" spans="1:7">
+    <row r="25" ht="18.75" spans="1:7">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -2381,7 +2397,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" ht="26.25" spans="1:5">
+    <row r="28" ht="18.75" spans="1:5">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -2392,7 +2408,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" ht="26.25" spans="1:2">
+    <row r="29" ht="18.75" spans="1:2">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -2400,7 +2416,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" ht="26.25" spans="1:2">
+    <row r="30" ht="18.75" spans="1:2">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -2408,7 +2424,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" ht="26.25" spans="1:2">
+    <row r="31" ht="18.75" spans="1:2">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -2416,7 +2432,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" ht="26.25" spans="1:2">
+    <row r="32" ht="18.75" spans="1:2">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -2424,7 +2440,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33" ht="26.25" spans="1:2">
+    <row r="33" ht="18.75" spans="1:2">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -2437,7 +2453,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" ht="26.25" spans="1:5">
+    <row r="36" ht="18.75" spans="1:5">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -2454,7 +2470,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="37" ht="26.25" spans="1:6">
+    <row r="37" ht="18.75" spans="1:6">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -2471,7 +2487,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="38" ht="26.25" spans="1:5">
+    <row r="38" ht="18.75" spans="1:5">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -2488,7 +2504,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" ht="26.25" spans="1:5">
+    <row r="39" ht="18.75" spans="1:5">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -2505,7 +2521,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" ht="26.25" spans="1:5">
+    <row r="40" ht="18.75" spans="1:5">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -2522,7 +2538,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" ht="26.25" spans="1:5">
+    <row r="41" ht="18.75" spans="1:5">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -2536,7 +2552,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="42" ht="26.25" spans="1:5">
+    <row r="42" ht="18.75" spans="1:5">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -2550,7 +2566,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="43" ht="26.25" spans="1:5">
+    <row r="43" ht="18.75" spans="1:5">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -2564,7 +2580,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="44" ht="26.25" spans="1:5">
+    <row r="44" ht="18.75" spans="1:5">
       <c r="A44" t="s">
         <v>28</v>
       </c>
@@ -2578,7 +2594,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" ht="26.25" spans="1:5">
+    <row r="45" ht="18.75" spans="1:5">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -2592,7 +2608,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="46" ht="26.25" spans="1:5">
+    <row r="46" ht="18.75" spans="1:5">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -2606,7 +2622,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" ht="26.25" spans="1:5">
+    <row r="47" ht="18.75" spans="1:5">
       <c r="A47" t="s">
         <v>28</v>
       </c>
@@ -2620,7 +2636,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" ht="26.25" spans="1:5">
+    <row r="48" ht="18.75" spans="1:5">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -2639,7 +2655,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" ht="26.25" spans="1:5">
+    <row r="51" ht="18.75" spans="1:5">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -2653,7 +2669,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" ht="26.25" spans="1:5">
+    <row r="52" ht="18.75" spans="1:5">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -2667,7 +2683,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" ht="26.25" spans="1:5">
+    <row r="53" ht="18.75" spans="1:5">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -2681,7 +2697,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" ht="26.25" spans="1:5">
+    <row r="54" ht="18.75" spans="1:5">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -2692,7 +2708,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="55" ht="69.4" spans="1:5">
+    <row r="55" ht="75" spans="1:5">
       <c r="A55" t="s">
         <v>28</v>
       </c>
@@ -2703,7 +2719,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="56" ht="55.5" spans="1:5">
+    <row r="56" ht="60" spans="1:5">
       <c r="A56" t="s">
         <v>28</v>
       </c>
@@ -2714,7 +2730,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="57" ht="55.5" spans="1:5">
+    <row r="57" ht="60" spans="1:5">
       <c r="A57" t="s">
         <v>28</v>
       </c>
@@ -2725,7 +2741,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="58" ht="55.5" spans="1:5">
+    <row r="58" ht="60" spans="1:5">
       <c r="A58" t="s">
         <v>28</v>
       </c>
@@ -2736,7 +2752,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" ht="55.5" spans="1:5">
+    <row r="59" ht="60" spans="1:5">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -2747,7 +2763,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="60" ht="55.5" spans="1:5">
+    <row r="60" ht="60" spans="1:5">
       <c r="A60" t="s">
         <v>28</v>
       </c>
@@ -2761,6 +2777,43 @@
     <row r="62" spans="5:5">
       <c r="E62" t="s">
         <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
